--- a/public/data/contract_addons.xlsx
+++ b/public/data/contract_addons.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,13 +427,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>9a4b43b3-8852-4639-999f-918ad49d8769</v>
+        <v>7ddb91dd-af4a-4af5-bea7-8ab21dcdfd5c</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -453,13 +453,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0e9a5b1b-f234-4adf-8848-4033504a98be</v>
+        <v>93742c9d-ef2f-4e05-aea8-e0e2b172c5b2</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
         <v>CTR-001-001</v>
@@ -479,94 +479,94 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>9e668785-a2df-472d-a03f-33d95616c688</v>
+        <v>3745e457-5513-477d-9d4f-dae48dbfeb92</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E4" t="str">
-        <v>Dedicated Vehicle</v>
+        <v>Photography</v>
       </c>
       <c r="F4" t="str">
-        <v>VIP Lounge Access</v>
+        <v>Aerial Photography Package</v>
       </c>
       <c r="G4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H4" t="str">
-        <v>Private charter lounge</v>
+        <v>Charter scenic flight with photographer</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>fb98c499-a5c4-4b1f-b3c1-fe9dfcd30c84</v>
+        <v>26fe8707-6695-481a-8bc3-3aad108fdcf2</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E5" t="str">
         <v>Dedicated Vehicle</v>
       </c>
       <c r="F5" t="str">
-        <v>Airport Transfer SUV</v>
+        <v>VIP Lounge Access</v>
       </c>
       <c r="G5">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Private charter lounge</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5b68a75f-d500-4228-a481-32b9fc441bda</v>
+        <v>89a08344-e343-44f9-806f-7f9ad7326402</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E6" t="str">
         <v>Dedicated Vehicle</v>
       </c>
       <c r="F6" t="str">
-        <v>VIP Lounge Access</v>
+        <v>Luxury Transfer</v>
       </c>
       <c r="G6">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="H6" t="str">
-        <v>TMA Lounge included for suites</v>
+        <v>Yacht transfer from airport</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2307a68e-4586-46fc-91e3-8a04e71075fe</v>
+        <v>b7b65883-8b55-4f08-a8bd-1b68003ae3df</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E7" t="str">
         <v>Dedicated Vehicle</v>
@@ -575,50 +575,50 @@
         <v>Airport Transfer SUV</v>
       </c>
       <c r="G7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H7" t="str">
-        <v>Meet &amp; greet included</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>f58f0929-4685-4c97-b9ea-cc6f5e6bb877</v>
+        <v>7310acbf-fdfa-4460-bfd3-62a5de9fdaa1</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E8" t="str">
-        <v>Photography</v>
+        <v>Dedicated Vehicle</v>
       </c>
       <c r="F8" t="str">
-        <v>Aerial Photography Package</v>
+        <v>VIP Lounge Access</v>
       </c>
       <c r="G8">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="H8" t="str">
-        <v>20-minute scenic flight with photographer</v>
+        <v>Marriott Bonvoy Platinum lounge</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>fe434d19-6616-4cef-be82-6a115bb30975</v>
+        <v>a3eddab7-e847-4b9e-a137-764bc85658b0</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E9" t="str">
         <v>Dedicated Vehicle</v>
@@ -627,67 +627,223 @@
         <v>VIP Lounge Access</v>
       </c>
       <c r="G9">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H9" t="str">
-        <v>Anantara lounge</v>
+        <v>TMA Lounge included for suites</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>052a3bda-f61f-4321-84b0-d141e8cd81c5</v>
+        <v>55bc317b-7721-47c4-8a97-791d7261e0c1</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E10" t="str">
         <v>Dedicated Vehicle</v>
       </c>
       <c r="F10" t="str">
-        <v>Airport Transfer Van</v>
+        <v>Airport Transfer SUV</v>
       </c>
       <c r="G10">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H10" t="str">
-        <v>Group transfer vehicle</v>
+        <v>Meet &amp; greet included</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>605ea9e5-fc59-4dd2-a032-aae82a851d30</v>
+        <v>6757589b-f0e9-4ca6-810d-48563e732a9a</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Photography</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Aerial Photography Package</v>
+      </c>
+      <c r="G11">
+        <v>350</v>
+      </c>
+      <c r="H11" t="str">
+        <v>20-minute scenic flight with photographer</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>5c71346c-172f-4603-8f9d-51c60340be15</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D12" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Dedicated Vehicle</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Luxury Yacht Transfer</v>
+      </c>
+      <c r="G12">
+        <v>500</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Signed charter luxury option</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>a794b50c-47c9-4bf3-be52-91dddbf66325</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D13" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Dedicated Vehicle</v>
+      </c>
+      <c r="F13" t="str">
+        <v>VIP Lounge Access</v>
+      </c>
+      <c r="G13">
+        <v>180</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Anantara lounge</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>a7c33d1f-7b56-4aaf-9cbd-ba793485fe4c</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D14" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Dedicated Vehicle</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Airport Transfer Van</v>
+      </c>
+      <c r="G14">
+        <v>60</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Group transfer vehicle</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>c4706d88-66a7-44ba-a0d4-e2d949f05bd1</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D15" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Photography</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Sunset Scenic Flight</v>
+      </c>
+      <c r="G15">
+        <v>280</v>
+      </c>
+      <c r="H15" t="str">
+        <v>30-min scenic flight at golden hour</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>c6d3c821-590b-417a-a39f-a6c7f3e30857</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D16" t="str">
         <v>CTR-009-001</v>
       </c>
-      <c r="E11" t="str">
-        <v>Dedicated Vehicle</v>
-      </c>
-      <c r="F11" t="str">
+      <c r="E16" t="str">
+        <v>Dedicated Vehicle</v>
+      </c>
+      <c r="F16" t="str">
         <v>Luxury Speedboat Upgrade</v>
       </c>
-      <c r="G11">
+      <c r="G16">
         <v>250</v>
       </c>
-      <c r="H11" t="str">
+      <c r="H16" t="str">
         <v>Private yacht-style transfer</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>9ea7c4b6-d16a-486c-929d-95320a8676bd</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-010-001</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Dedicated Vehicle</v>
+      </c>
+      <c r="F17" t="str">
+        <v>VIP Lounge Access</v>
+      </c>
+      <c r="G17">
+        <v>190</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Soneva private lounge</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
   </ignoredErrors>
 </worksheet>
 </file>